--- a/CostarExport.xlsx
+++ b/CostarExport.xlsx
@@ -8,74 +8,36 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Business\TOCOnnect\Code\Python Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C908C6F3-681D-475B-956D-1624DD437249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32D7E4FA-BB51-4B26-8608-338B9B1286EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-16860" yWindow="1790" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Export121725" sheetId="1" r:id="rId1"/>
+    <sheet name="Export010826" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+  <si>
+    <t>Postal Code</t>
+  </si>
+  <si>
+    <t>Region Name</t>
+  </si>
   <si>
     <t>City</t>
   </si>
   <si>
-    <t>Submarket Name</t>
-  </si>
-  <si>
-    <t>Building Class</t>
+    <t>Year Built</t>
   </si>
   <si>
     <t>RBA</t>
   </si>
   <si>
-    <t>Number Of Stories</t>
-  </si>
-  <si>
-    <t>Typical Floor Size</t>
-  </si>
-  <si>
-    <t>Year Built</t>
+    <t>Ceiling Ht</t>
   </si>
   <si>
     <t>Total Available Space (SF)</t>
@@ -84,82 +46,139 @@
     <t>Direct Available Space</t>
   </si>
   <si>
-    <t>Percent Leased</t>
+    <t>Number Of Loading Docks</t>
+  </si>
+  <si>
+    <t>Drive Ins</t>
   </si>
   <si>
     <t>Rent/SF/Yr</t>
   </si>
   <si>
-    <t>5925 Airport Rd</t>
+    <t>96 Inspire Blvd</t>
+  </si>
+  <si>
+    <t>L6R 3Y2</t>
+  </si>
+  <si>
+    <t>Peel</t>
+  </si>
+  <si>
+    <t>Brampton</t>
+  </si>
+  <si>
+    <t>36'6"</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>$14.50</t>
+  </si>
+  <si>
+    <t>8705 Torbram Rd</t>
+  </si>
+  <si>
+    <t>L6T 3V9</t>
+  </si>
+  <si>
+    <t>24'0"</t>
+  </si>
+  <si>
+    <t>3/10'0"w x 12'0"h</t>
+  </si>
+  <si>
+    <t>$15.00 - 18.50</t>
+  </si>
+  <si>
+    <t>2550 Stanfield Rd</t>
+  </si>
+  <si>
+    <t>L4Y 1S2</t>
   </si>
   <si>
     <t>Mississauga</t>
   </si>
   <si>
-    <t>Airport Corp Centre/Airport</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>$13.50</t>
-  </si>
-  <si>
-    <t>5935 Airport Rd</t>
-  </si>
-  <si>
-    <t>6303 Airport Rd</t>
-  </si>
-  <si>
-    <t>10 Carlson Crt</t>
-  </si>
-  <si>
-    <t>Toronto</t>
-  </si>
-  <si>
-    <t>$21.50</t>
-  </si>
-  <si>
-    <t>5090 Commerce Blvd</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>$25.47 - 31.12 (Est.)</t>
-  </si>
-  <si>
-    <t>5110 Creekbank Rd</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>$17.46 - 21.34 (Est.)</t>
-  </si>
-  <si>
-    <t>5090 Explorer Dr</t>
-  </si>
-  <si>
-    <t>$18.50</t>
-  </si>
-  <si>
-    <t>5520 Explorer Dr</t>
-  </si>
-  <si>
-    <t>$19.50</t>
-  </si>
-  <si>
-    <t>5560 Explorer Dr</t>
-  </si>
-  <si>
-    <t>$18.50 - 19.50</t>
+    <t>34'0"</t>
+  </si>
+  <si>
+    <t>$13.95</t>
+  </si>
+  <si>
+    <t>6450 Cantay Rd</t>
+  </si>
+  <si>
+    <t>L5R 4J6</t>
+  </si>
+  <si>
+    <t>30'0"</t>
+  </si>
+  <si>
+    <t>1574 Eagle St N</t>
+  </si>
+  <si>
+    <t>N3H 4S5</t>
+  </si>
+  <si>
+    <t>Waterloo</t>
+  </si>
+  <si>
+    <t>Cambridge</t>
+  </si>
+  <si>
+    <t>32'6"</t>
+  </si>
+  <si>
+    <t>4/16'0"w x 18'0"h</t>
+  </si>
+  <si>
+    <t>$14.95</t>
+  </si>
+  <si>
+    <t>1080 Southgate Dr</t>
+  </si>
+  <si>
+    <t>N1L 0G5</t>
+  </si>
+  <si>
+    <t>Wellington</t>
+  </si>
+  <si>
+    <t>Guelph</t>
+  </si>
+  <si>
+    <t>40'0"</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>$15.50</t>
+  </si>
+  <si>
+    <t>120 Allendale Rd</t>
+  </si>
+  <si>
+    <t>N3H 4R7</t>
+  </si>
+  <si>
+    <t>$8.71 - 10.65 (Est.)</t>
+  </si>
+  <si>
+    <t>220 Pinebush Rd</t>
+  </si>
+  <si>
+    <t>N1T 1Z6</t>
+  </si>
+  <si>
+    <t>$9.93 - 12.13 (Est.)</t>
+  </si>
+  <si>
+    <t>Address</t>
   </si>
   <si>
     <t>No</t>
-  </si>
-  <si>
-    <t>Address</t>
   </si>
 </sst>
 </file>
@@ -179,18 +198,12 @@
       <name val="Calibri"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -205,14 +218,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="4" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -515,68 +525,66 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M9"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5" style="6" customWidth="1"/>
-    <col min="2" max="2" width="20.7265625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.453125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.453125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.26953125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="16.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.453125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.7265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="7.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.7265625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="24" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="21" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.26953125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.81640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1" s="3" t="s">
+      <c r="A1" t="s">
+        <v>52</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>7</v>
       </c>
       <c r="K1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" cm="1">
-        <f t="array" ref="A2">IF(COUNTIF($B$2:B2,B2)=1,MAX($A$1:A1)+1, _xlfn.XLOOKUP(B2,$B1:B$2,$A1:A$2))</f>
+      <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
@@ -591,41 +599,40 @@
       <c r="E2" t="s">
         <v>14</v>
       </c>
-      <c r="F2">
-        <v>163312</v>
-      </c>
-      <c r="G2" s="1">
-        <v>10</v>
-      </c>
-      <c r="H2">
-        <v>16331</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1982</v>
+      <c r="F2" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G2">
+        <v>162500</v>
+      </c>
+      <c r="H2" t="s">
+        <v>15</v>
+      </c>
+      <c r="I2">
+        <v>162500</v>
       </c>
       <c r="J2">
-        <v>102100</v>
-      </c>
-      <c r="K2">
-        <v>102100</v>
-      </c>
-      <c r="L2" s="2">
-        <v>69.73</v>
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <v>22</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3" s="6" cm="1">
-        <f t="array" ref="A3">IF(COUNTIF($B$2:B3,B3)=1,MAX($A$1:A2)+1, _xlfn.XLOOKUP(B3,$B2:B$2,$A2:A$2))</f>
+      <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
         <v>13</v>
@@ -633,323 +640,269 @@
       <c r="E3" t="s">
         <v>14</v>
       </c>
-      <c r="F3">
-        <v>183952</v>
-      </c>
-      <c r="G3" s="1">
-        <v>11</v>
-      </c>
-      <c r="H3">
-        <v>18395</v>
-      </c>
-      <c r="I3" s="1">
-        <v>1982</v>
+      <c r="F3" s="1">
+        <v>1980</v>
+      </c>
+      <c r="G3">
+        <v>296289</v>
+      </c>
+      <c r="H3" t="s">
+        <v>20</v>
+      </c>
+      <c r="I3">
+        <v>201095</v>
       </c>
       <c r="J3">
-        <v>68492</v>
-      </c>
-      <c r="K3">
-        <v>42148</v>
-      </c>
-      <c r="L3" s="2">
-        <v>77.09</v>
+        <v>201095</v>
+      </c>
+      <c r="K3" s="1">
+        <v>26</v>
+      </c>
+      <c r="L3" t="s">
+        <v>21</v>
       </c>
       <c r="M3" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4" s="6" cm="1">
-        <f t="array" ref="A4">IF(COUNTIF($B$2:B4,B4)=1,MAX($A$1:A3)+1, _xlfn.XLOOKUP(B4,$B$2:B3,$A$2:A3))</f>
+      <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
         <v>13</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
-      </c>
-      <c r="F4">
-        <v>81315</v>
-      </c>
-      <c r="G4" s="1">
-        <v>5</v>
-      </c>
-      <c r="H4">
-        <v>16263</v>
-      </c>
-      <c r="I4" s="1">
-        <v>1975</v>
+        <v>25</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1964</v>
+      </c>
+      <c r="G4">
+        <v>340314</v>
+      </c>
+      <c r="H4" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4">
+        <v>238501</v>
       </c>
       <c r="J4">
-        <v>46769</v>
-      </c>
-      <c r="K4">
-        <v>46769</v>
-      </c>
-      <c r="L4" s="2">
-        <v>42.48</v>
+        <v>238501</v>
+      </c>
+      <c r="K4" s="1">
+        <v>25</v>
+      </c>
+      <c r="L4" t="s">
+        <v>16</v>
       </c>
       <c r="M4" t="s">
-        <v>15</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5" s="6" cm="1">
-        <f t="array" ref="A5">IF(COUNTIF($B$2:B5,B5)=1,MAX($A$1:A4)+1, _xlfn.XLOOKUP(B5,$B$2:B4,$A$2:A4))</f>
+      <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="D5" t="s">
         <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5">
-        <v>159259</v>
-      </c>
-      <c r="G5" s="1">
-        <v>8</v>
-      </c>
-      <c r="H5">
-        <v>19907</v>
-      </c>
-      <c r="I5" s="1">
-        <v>1985</v>
+        <v>25</v>
+      </c>
+      <c r="F5" s="1">
+        <v>2003</v>
+      </c>
+      <c r="G5">
+        <v>288246</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5">
+        <v>288246</v>
       </c>
       <c r="J5">
-        <v>48876</v>
-      </c>
-      <c r="K5">
-        <v>26506</v>
-      </c>
-      <c r="L5" s="2">
-        <v>87.84</v>
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <v>24</v>
+      </c>
+      <c r="L5" t="s">
+        <v>21</v>
       </c>
       <c r="M5" t="s">
-        <v>20</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6" s="6" cm="1">
-        <f t="array" ref="A6">IF(COUNTIF($B$2:B6,B6)=1,MAX($A$1:A5)+1, _xlfn.XLOOKUP(B6,$B$2:B5,$A$2:A5))</f>
+      <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F6">
-        <v>42748</v>
-      </c>
-      <c r="G6" s="1">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>21374</v>
-      </c>
-      <c r="I6" s="1">
-        <v>1999</v>
+        <v>34</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2025</v>
+      </c>
+      <c r="G6">
+        <v>158000</v>
+      </c>
+      <c r="H6" t="s">
+        <v>35</v>
+      </c>
+      <c r="I6">
+        <v>158000</v>
       </c>
       <c r="J6">
-        <v>21374</v>
-      </c>
-      <c r="K6">
-        <v>0</v>
-      </c>
-      <c r="L6" s="2">
-        <v>100</v>
+        <v>158000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>9</v>
+      </c>
+      <c r="L6" t="s">
+        <v>36</v>
       </c>
       <c r="M6" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7" s="6" cm="1">
-        <f t="array" ref="A7">IF(COUNTIF($B$2:B7,B7)=1,MAX($A$1:A6)+1, _xlfn.XLOOKUP(B7,$B$2:B6,$A$2:A6))</f>
+      <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>39</v>
       </c>
       <c r="D7" t="s">
-        <v>12</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7">
-        <v>101000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>101000</v>
-      </c>
-      <c r="I7" s="1">
-        <v>2005</v>
+        <v>41</v>
+      </c>
+      <c r="F7" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G7">
+        <v>444186</v>
+      </c>
+      <c r="H7" t="s">
+        <v>42</v>
+      </c>
+      <c r="I7">
+        <v>444186</v>
       </c>
       <c r="J7">
-        <v>94962</v>
-      </c>
-      <c r="K7">
-        <v>0</v>
-      </c>
-      <c r="L7" s="2">
-        <v>100</v>
+        <v>444186</v>
+      </c>
+      <c r="K7" s="1">
+        <v>61</v>
+      </c>
+      <c r="L7" t="s">
+        <v>43</v>
       </c>
       <c r="M7" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8" s="6" cm="1">
-        <f t="array" ref="A8">IF(COUNTIF($B$2:B8,B8)=1,MAX($A$1:A7)+1, _xlfn.XLOOKUP(B8,$B$2:B7,$A$2:A7))</f>
+      <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>46</v>
       </c>
       <c r="D8" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E8" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8">
-        <v>169154</v>
-      </c>
-      <c r="G8" s="1">
-        <v>10</v>
-      </c>
-      <c r="H8">
-        <v>19600</v>
-      </c>
-      <c r="I8" s="1">
-        <v>1988</v>
+        <v>34</v>
+      </c>
+      <c r="F8" s="1">
+        <v>2024</v>
+      </c>
+      <c r="G8">
+        <v>328068</v>
+      </c>
+      <c r="H8" t="s">
+        <v>42</v>
+      </c>
+      <c r="I8">
+        <v>328068</v>
       </c>
       <c r="J8">
-        <v>50930</v>
-      </c>
-      <c r="K8">
-        <v>50930</v>
-      </c>
-      <c r="L8" s="2">
-        <v>80.22</v>
+        <v>328068</v>
+      </c>
+      <c r="K8" s="1">
+        <v>61</v>
+      </c>
+      <c r="L8" t="s">
+        <v>43</v>
       </c>
       <c r="M8" t="s">
-        <v>28</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9" s="6" cm="1">
-        <f t="array" ref="A9">IF(COUNTIF($B$2:B9,B9)=1,MAX($A$1:A8)+1, _xlfn.XLOOKUP(B9,$B$2:B8,$A$2:A8))</f>
+      <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>48</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>49</v>
       </c>
       <c r="D9" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F9">
-        <v>101116</v>
-      </c>
-      <c r="G9" s="1">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>25500</v>
-      </c>
-      <c r="I9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J9">
-        <v>58604</v>
-      </c>
-      <c r="K9">
-        <v>58604</v>
-      </c>
-      <c r="L9" s="2">
-        <v>45.41</v>
+        <v>34</v>
+      </c>
+      <c r="F9" s="1">
+        <v>2023</v>
+      </c>
+      <c r="G9">
+        <v>209075</v>
+      </c>
+      <c r="H9" t="s">
+        <v>42</v>
+      </c>
+      <c r="K9" s="1">
+        <v>58</v>
+      </c>
+      <c r="L9" t="s">
+        <v>43</v>
       </c>
       <c r="M9" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10" s="6" cm="1">
-        <f t="array" ref="A10">IF(COUNTIF($B$2:B10,B10)=1,MAX($A$1:A9)+1, _xlfn.XLOOKUP(B10,$B$2:B9,$A$2:A9))</f>
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>31</v>
-      </c>
-      <c r="C10" t="s">
-        <v>12</v>
-      </c>
-      <c r="D10" t="s">
-        <v>13</v>
-      </c>
-      <c r="E10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10">
-        <v>126435</v>
-      </c>
-      <c r="G10" s="1">
-        <v>4</v>
-      </c>
-      <c r="H10">
-        <v>25246</v>
-      </c>
-      <c r="I10" s="1">
-        <v>2000</v>
-      </c>
-      <c r="J10">
-        <v>36996</v>
-      </c>
-      <c r="K10">
-        <v>36996</v>
-      </c>
-      <c r="L10" s="2">
-        <v>70.739999999999995</v>
-      </c>
-      <c r="M10" t="s">
-        <v>32</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/CostarExport.xlsx
+++ b/CostarExport.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Business\TOCOnnect\Code\Python Practice\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{23F20C08-E28C-438A-A002-3D24ADD0F8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1902D9AE-1FF6-404F-BDA6-0F6A2622FD77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>Direct Available Rate</t>
   </si>
   <si>
-    <t>Address</t>
-  </si>
-  <si>
     <t>245 Fairview Mall Dr</t>
   </si>
   <si>
@@ -144,6 +141,9 @@
   </si>
   <si>
     <t>4141 Yonge St</t>
+  </si>
+  <si>
+    <t>Property Address</t>
   </si>
 </sst>
 </file>
@@ -518,7 +518,7 @@
         <v>28</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>0</v>
@@ -562,7 +562,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2" t="s">
         <v>11</v>
@@ -609,7 +609,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
         <v>11</v>
@@ -844,7 +844,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C8" t="s">
         <v>11</v>
@@ -985,7 +985,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C11" t="s">
         <v>11</v>
@@ -1167,7 +1167,7 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
         <v>11</v>
